--- a/downloads/omnicraft_cost_calculator_template_en.xlsx
+++ b/downloads/omnicraft_cost_calculator_template_en.xlsx
@@ -703,13 +703,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1265,7 +1265,7 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>6. LABOR &amp; WORKSHOP OVERHEAD</t>
+          <t>6. CRAFTSMAN LABOR &amp; EQUIPMENT DEPRECIATION</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1320,118 +1320,117 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>3. Hourly workshop overhead (studio rent, electricity, wear)</t>
+          <t>3. Equipment / machine runtime on the item (T_mach)</t>
         </is>
       </c>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="5" t="n"/>
-      <c r="E34" s="23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F34" s="23" t="n"/>
+      <c r="E34" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F34" s="22" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>4. Fixed workshop overhead per item</t>
+          <t>4. Hourly equipment depreciation &amp; tooling wear</t>
         </is>
       </c>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="5" t="n"/>
-      <c r="E35" s="8" t="n">
+      <c r="E35" s="23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F35" s="23" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>5. Fixed workshop overhead per item</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL OVERHEAD &amp; DEPRECIATION (T × Hourly + Fixed)</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="n"/>
-      <c r="C36" s="19" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="19" t="n"/>
-      <c r="F36" s="20">
-        <f>ROUND(E31*E34+E35, 2)</f>
-        <v/>
-      </c>
+      <c r="F36" s="8" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL EQUIPMENT DEPRECIATION &amp; OVERHEAD (T_mach × Wear + Fixed)</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="n"/>
+      <c r="C37" s="19" t="n"/>
+      <c r="D37" s="19" t="n"/>
+      <c r="E37" s="19" t="n"/>
+      <c r="F37" s="20">
+        <f>ROUND(E34*E35+E36, 2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>7. TAXATION</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Revenue tax rate (e.g. 6.0% small business tax)</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="24" t="n">
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="24" t="n">
         <v>0.06</v>
       </c>
-      <c r="F38" s="24" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
+      <c r="F39" s="24" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>TOTAL SALES TAX (Price × Rate)</t>
         </is>
       </c>
-      <c r="B39" s="19" t="n"/>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="20">
-        <f>ROUND(F6*E38, 2)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="25" t="inlineStr">
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="19" t="n"/>
+      <c r="D40" s="19" t="n"/>
+      <c r="E40" s="19" t="n"/>
+      <c r="F40" s="20">
+        <f>ROUND(F6*E39, 2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
         <is>
           <t>8. FINAL UNIT ECONOMICS &amp; PROFIT DIAGNOSIS</t>
         </is>
       </c>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="25" t="n"/>
-      <c r="D40" s="25" t="n"/>
-      <c r="E40" s="25" t="n"/>
-      <c r="F40" s="25" t="n"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>1. Manufacturing unit cost (materials + hardware + supplies + packaging + labor + overhead)</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="26">
-        <f>F14+F21+F27+F29+F33+F36</f>
-        <v/>
-      </c>
+      <c r="B41" s="25" t="n"/>
+      <c r="C41" s="25" t="n"/>
+      <c r="D41" s="25" t="n"/>
+      <c r="E41" s="25" t="n"/>
+      <c r="F41" s="25" t="n"/>
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>2. Total cost of goods sold (including tax)</t>
+          <t>1. Manufacturing unit cost (materials + hardware + supplies + packaging + labor + wear)</t>
         </is>
       </c>
       <c r="B42" s="7" t="n"/>
@@ -1439,29 +1438,29 @@
       <c r="D42" s="7" t="n"/>
       <c r="E42" s="7" t="n"/>
       <c r="F42" s="26">
-        <f>F41+F39</f>
+        <f>F14+F21+F27+F29+F33+F37</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>3. Net business profit (Price - COGS)</t>
+          <t>2. Total cost of goods sold (including tax)</t>
         </is>
       </c>
       <c r="B43" s="7" t="n"/>
       <c r="C43" s="7" t="n"/>
       <c r="D43" s="7" t="n"/>
       <c r="E43" s="7" t="n"/>
-      <c r="F43" s="27">
-        <f>F6-F42</f>
+      <c r="F43" s="26">
+        <f>F42+F40</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>4. Craftsman take-home earnings (Labor + Net profit)</t>
+          <t>3. Net business profit (Price - COGS)</t>
         </is>
       </c>
       <c r="B44" s="7" t="n"/>
@@ -1469,130 +1468,146 @@
       <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="27">
-        <f>F33+F43</f>
+        <f>F6-F43</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>5. Effective hourly wage (Take-home earnings / T)</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="28">
-        <f>IF(E31&gt;0, ROUND(F44/E31, 2), 0)</f>
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>4. Craftsman take-home earnings (Labor + Net profit)</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="27">
+        <f>F33+F44</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>6. Net profit margin (Net profit / Price)</t>
+          <t>5. Effective hourly wage (Take-home earnings / T)</t>
         </is>
       </c>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="5" t="n"/>
       <c r="D46" s="5" t="n"/>
       <c r="E46" s="5" t="n"/>
-      <c r="F46" s="29">
-        <f>IF(F6&gt;0, F43/F6, 0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="30">
-        <f>IF(F43&lt;0, "🔴 Profit illusion: item sold at a loss. You work for free and subsidize materials!", IF(F45&lt;E32, "🟡 Hidden risk: effective hourly wage is below your base rate. Labor eats your margin.", "🟢 Healthy order: covers all expenses, pays fair craftsman wage, and earns net profit."))</f>
-        <v/>
-      </c>
-      <c r="B47" s="30" t="n"/>
-      <c r="C47" s="30" t="n"/>
-      <c r="D47" s="30" t="n"/>
-      <c r="E47" s="30" t="n"/>
-      <c r="F47" s="30" t="n"/>
-    </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="31" t="inlineStr">
+      <c r="F46" s="28">
+        <f>IF(E31&gt;0, ROUND(F45/E31, 2), 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>6. Net profit margin (Net profit / Price)</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="29">
+        <f>IF(F6&gt;0, F44/F6, 0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="30">
+        <f>IF(F44&lt;0, "🔴 Profit illusion: item sold at a loss. You work for free and subsidize materials!", IF(F47&lt;0.15, "🟡 Hidden risk: net margin is below 15%. Any material waste or defect will wipe out your profit.", "🟢 Healthy order: covers all expenses, pays fair craftsman wage, and earns net profit."))</f>
+        <v/>
+      </c>
+      <c r="B48" s="30" t="n"/>
+      <c r="C48" s="30" t="n"/>
+      <c r="D48" s="30" t="n"/>
+      <c r="E48" s="30" t="n"/>
+      <c r="F48" s="30" t="n"/>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="31" t="inlineStr">
         <is>
           <t>WANT PROFESSIONAL WORKSHOP ACCOUNTING? TRY OMNICRAFT ERP</t>
         </is>
       </c>
-      <c r="B49" s="31" t="n"/>
-      <c r="C49" s="31" t="n"/>
-      <c r="D49" s="31" t="n"/>
-      <c r="E49" s="31" t="n"/>
-      <c r="F49" s="31" t="n"/>
-    </row>
-    <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="32" t="inlineStr">
+      <c r="B50" s="31" t="n"/>
+      <c r="C50" s="31" t="n"/>
+      <c r="D50" s="31" t="n"/>
+      <c r="E50" s="31" t="n"/>
+      <c r="F50" s="31" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="32" t="inlineStr">
         <is>
           <t>Autonomous local desktop ERP system for craftsmen and small manufacturing workshops</t>
         </is>
       </c>
-      <c r="B50" s="32" t="n"/>
-      <c r="C50" s="32" t="n"/>
-      <c r="D50" s="32" t="n"/>
-      <c r="E50" s="32" t="n"/>
-      <c r="F50" s="32" t="n"/>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="33" t="inlineStr">
+      <c r="B51" s="32" t="n"/>
+      <c r="C51" s="32" t="n"/>
+      <c r="D51" s="32" t="n"/>
+      <c r="E51" s="32" t="n"/>
+      <c r="F51" s="32" t="n"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="33" t="inlineStr">
         <is>
           <t>Download free from the official website: https://omnicraft-erp.com/</t>
         </is>
       </c>
-      <c r="B51" s="33" t="n"/>
-      <c r="C51" s="33" t="n"/>
-      <c r="D51" s="33" t="n"/>
-      <c r="E51" s="33" t="n"/>
-      <c r="F51" s="33" t="n"/>
+      <c r="B52" s="33" t="n"/>
+      <c r="C52" s="33" t="n"/>
+      <c r="D52" s="33" t="n"/>
+      <c r="E52" s="33" t="n"/>
+      <c r="F52" s="33" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
-  <mergeCells count="50">
-    <mergeCell ref="A39:E39"/>
+  <mergeCells count="52">
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A35:D35"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A38:D38"/>
     <mergeCell ref="A45:E45"/>
     <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E39:F39"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E35:F35"/>
-    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A31:D31"/>
-    <mergeCell ref="E38:F38"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A52:F52"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="E36:F36"/>
     <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="A1:F1"/>
@@ -1601,11 +1616,12 @@
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A40:E40"/>
     <mergeCell ref="A32:D32"/>
     <mergeCell ref="A7:F7"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
